--- a/data/trans_dic/IP12_R2_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP12_R2_2023-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por síntomas 2023</t>
+          <t>Menores que limitaron su actividad por síntomas 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,17; 10,74</t>
+          <t>2,91; 10,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,06; 7,33</t>
+          <t>1,25; 7,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,68; 7,34</t>
+          <t>2,57; 7,42</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,25; 7,63</t>
+          <t>1,23; 7,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,98; 14,48</t>
+          <t>4,21; 15,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,43; 9,51</t>
+          <t>3,22; 9,09</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,98; 9,45</t>
+          <t>1,0; 10,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,79; 13,08</t>
+          <t>1,98; 12,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,09; 8,96</t>
+          <t>2,08; 9,37</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,73; 5,87</t>
+          <t>1,56; 5,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,09; 8,36</t>
+          <t>3,13; 8,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,9; 6,36</t>
+          <t>2,77; 6,24</t>
         </is>
       </c>
     </row>
@@ -771,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,01; 13,7</t>
+          <t>5,3; 13,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,93; 12,54</t>
+          <t>4,05; 13,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,19; 11,57</t>
+          <t>5,08; 10,92</t>
         </is>
       </c>
     </row>
@@ -821,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,47; 10,24</t>
+          <t>1,55; 9,88</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,89; 12,06</t>
+          <t>1,87; 11,89</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,56; 8,89</t>
+          <t>2,56; 8,93</t>
         </is>
       </c>
     </row>
@@ -871,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,65; 6,53</t>
+          <t>3,73; 6,51</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,32; 7,4</t>
+          <t>4,31; 7,46</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,38; 6,51</t>
+          <t>4,38; 6,54</t>
         </is>
       </c>
     </row>
@@ -905,4 +906,602 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que limitaron su actividad por síntomas 2023 (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>6299</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4579</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>10877</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>3038; 11130</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1706; 10449</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>6196; 17910</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>3277</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>7672</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>10949</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>1161; 7056</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>4027; 14577</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>6128; 17288</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1841</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>3460</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>5301</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>520; 5557</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1261; 8221</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2409; 10842</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>7390</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>11736</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>19126</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>3399; 12454</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>6834; 18587</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>12096; 27240</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>10277</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>11642</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>21919</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>6328; 16353</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>6578; 21292</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>14331; 30807</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>3050</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>3981</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>7030</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>1071; 6809</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>1349; 8564</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>3610; 12583</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>32134</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>43069</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>75204</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>24518; 42784</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>32287; 55856</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>61589; 91940</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP12_R2_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP12_R2_2023-Clase-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por síntomas 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores que en las últimas 2 semanas limitaron su actividad por síntomas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,91; 10,65</t>
+          <t>3,12; 11,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,25; 7,63</t>
+          <t>1,39; 7,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,57; 7,42</t>
+          <t>2,75; 7,41</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,23; 7,45</t>
+          <t>1,18; 7,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,21; 15,25</t>
+          <t>3,98; 14,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,22; 9,09</t>
+          <t>3,3; 9,44</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 10,71</t>
+          <t>0,98; 9,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,98; 12,87</t>
+          <t>1,68; 12,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,08; 9,37</t>
+          <t>1,85; 8,67</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,56; 5,71</t>
+          <t>1,7; 5,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,13; 8,52</t>
+          <t>3,14; 8,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,77; 6,24</t>
+          <t>2,74; 6,28</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,3; 13,69</t>
+          <t>4,87; 13,28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,05; 13,09</t>
+          <t>3,8; 12,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,08; 10,92</t>
+          <t>5,06; 11,5</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,55; 9,88</t>
+          <t>1,51; 9,67</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,87; 11,89</t>
+          <t>2,05; 11,89</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,56; 8,93</t>
+          <t>2,23; 8,41</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,73; 6,51</t>
+          <t>3,72; 6,55</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,31; 7,46</t>
+          <t>4,27; 7,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,38; 6,54</t>
+          <t>4,42; 6,53</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por síntomas 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores que en las últimas 2 semanas limitaron su actividad por síntomas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3038; 11130</t>
+          <t>3260; 11655</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1706; 10449</t>
+          <t>1905; 10192</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6196; 17910</t>
+          <t>6648; 17880</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1161; 7056</t>
+          <t>1115; 7408</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4027; 14577</t>
+          <t>3805; 13493</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6128; 17288</t>
+          <t>6270; 17955</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>520; 5557</t>
+          <t>507; 4873</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1261; 8221</t>
+          <t>1074; 7837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2409; 10842</t>
+          <t>2138; 10037</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3399; 12454</t>
+          <t>3709; 12903</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6834; 18587</t>
+          <t>6857; 18633</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12096; 27240</t>
+          <t>11971; 27405</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>6328; 16353</t>
+          <t>5813; 15864</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>6578; 21292</t>
+          <t>6185; 20882</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>14331; 30807</t>
+          <t>14259; 32422</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1071; 6809</t>
+          <t>1041; 6665</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1349; 8564</t>
+          <t>1474; 8561</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3610; 12583</t>
+          <t>3136; 11847</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>24518; 42784</t>
+          <t>24477; 43048</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>32287; 55856</t>
+          <t>32006; 56607</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>61589; 91940</t>
+          <t>62203; 91862</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP12_R2_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP12_R2_2023-Clase-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,69%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,12; 11,16</t>
+          <t>1,02; 7,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,39; 7,44</t>
+          <t>3,38; 11,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,75; 7,41</t>
+          <t>2,8; 7,54</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,71%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,18; 7,82</t>
+          <t>4,11; 15,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,98; 14,12</t>
+          <t>1,16; 7,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,3; 9,44</t>
+          <t>3,4; 9,65</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,98; 9,4</t>
+          <t>1,7; 13,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,68; 12,27</t>
+          <t>0,8; 8,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,85; 8,67</t>
+          <t>2,01; 9,03</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,65%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,7; 5,92</t>
+          <t>3,02; 8,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,14; 8,54</t>
+          <t>2,16; 6,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,74; 6,28</t>
+          <t>3,13; 6,8</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,64%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,87; 13,28</t>
+          <t>3,99; 13,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,8; 12,84</t>
+          <t>4,64; 12,85</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,06; 11,5</t>
+          <t>5,13; 11,7</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,44%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,51; 9,67</t>
+          <t>1,95; 13,07</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,05; 11,89</t>
+          <t>1,64; 11,6</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,23; 8,41</t>
+          <t>2,74; 9,61</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,48%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,72; 6,55</t>
+          <t>4,35; 7,6</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,27; 7,56</t>
+          <t>3,9; 6,65</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,42; 6,53</t>
+          <t>4,49; 6,67</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -986,12 +986,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6299</t>
+          <t>4049</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4579</t>
+          <t>6526</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10877</t>
+          <t>10574</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3260; 11655</t>
+          <t>1254; 8662</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1905; 10192</t>
+          <t>3484; 11503</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6648; 17880</t>
+          <t>6305; 17013</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>3277</t>
+          <t>7598</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>7672</t>
+          <t>3130</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10949</t>
+          <t>10728</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1115; 7408</t>
+          <t>3759; 13964</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3805; 13493</t>
+          <t>1119; 7212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6270; 17955</t>
+          <t>6387; 18131</t>
         </is>
       </c>
     </row>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1841</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3460</t>
+          <t>1731</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>4836</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>507; 4873</t>
+          <t>968; 7716</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1074; 7837</t>
+          <t>427; 4781</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2138; 10037</t>
+          <t>2217; 9973</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>7390</t>
+          <t>10601</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>11736</t>
+          <t>7104</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>19126</t>
+          <t>17705</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3709; 12903</t>
+          <t>6092; 16916</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6857; 18633</t>
+          <t>3869; 12214</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11971; 27405</t>
+          <t>11937; 25878</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>17</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>10277</t>
+          <t>10784</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>11642</t>
+          <t>9618</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21919</t>
+          <t>20402</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5813; 15864</t>
+          <t>5909; 19385</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>6185; 20882</t>
+          <t>5513; 15256</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>14259; 32422</t>
+          <t>13696; 31232</t>
         </is>
       </c>
     </row>
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>3050</t>
+          <t>4067</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3981</t>
+          <t>3480</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7030</t>
+          <t>7547</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1041; 6665</t>
+          <t>1330; 8928</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1474; 8561</t>
+          <t>1155; 8159</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3136; 11847</t>
+          <t>3799; 13329</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>53</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>32134</t>
+          <t>40203</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>43069</t>
+          <t>31589</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>75204</t>
+          <t>71792</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>24477; 43048</t>
+          <t>30009; 52364</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>32006; 56607</t>
+          <t>24218; 41283</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>62203; 91862</t>
+          <t>58828; 87431</t>
         </is>
       </c>
     </row>
